--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/NEVADA_2016.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/NEVADA_2016.xlsx
@@ -2983,7 +2983,7 @@
         <v>169</v>
       </c>
       <c r="D146">
-        <v>0.009540476459297731</v>
+        <v>0.009540476459297733</v>
       </c>
     </row>
     <row r="147">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C168">
@@ -3829,7 +3829,7 @@
         <v>16</v>
       </c>
       <c r="D193">
-        <v>0.0009032403748447555</v>
+        <v>0.0009032403748447556</v>
       </c>
     </row>
     <row r="194">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C294">
@@ -6313,7 +6313,7 @@
         <v>16</v>
       </c>
       <c r="D331">
-        <v>0.0009032403748447555</v>
+        <v>0.0009032403748447556</v>
       </c>
     </row>
     <row r="332">
@@ -6583,7 +6583,7 @@
         <v>16</v>
       </c>
       <c r="D346">
-        <v>0.0009032403748447555</v>
+        <v>0.0009032403748447556</v>
       </c>
     </row>
     <row r="347">
@@ -7033,7 +7033,7 @@
         <v>16</v>
       </c>
       <c r="D371">
-        <v>0.0009032403748447555</v>
+        <v>0.0009032403748447556</v>
       </c>
     </row>
     <row r="372">
@@ -7699,7 +7699,7 @@
         <v>165</v>
       </c>
       <c r="D408">
-        <v>0.009314666365586541</v>
+        <v>0.009314666365586539</v>
       </c>
     </row>
     <row r="409">
@@ -8725,7 +8725,7 @@
         <v>16</v>
       </c>
       <c r="D465">
-        <v>0.0009032403748447555</v>
+        <v>0.0009032403748447556</v>
       </c>
     </row>
     <row r="466">
@@ -9013,7 +9013,7 @@
         <v>16</v>
       </c>
       <c r="D481">
-        <v>0.0009032403748447555</v>
+        <v>0.0009032403748447556</v>
       </c>
     </row>
     <row r="482">
@@ -9085,7 +9085,7 @@
         <v>16</v>
       </c>
       <c r="D485">
-        <v>0.0009032403748447555</v>
+        <v>0.0009032403748447556</v>
       </c>
     </row>
     <row r="486">
@@ -9139,7 +9139,7 @@
         <v>16</v>
       </c>
       <c r="D488">
-        <v>0.0009032403748447555</v>
+        <v>0.0009032403748447556</v>
       </c>
     </row>
     <row r="489">
@@ -11227,7 +11227,7 @@
         <v>16</v>
       </c>
       <c r="D604">
-        <v>0.0009032403748447555</v>
+        <v>0.0009032403748447556</v>
       </c>
     </row>
     <row r="605">
@@ -11821,7 +11821,7 @@
         <v>170</v>
       </c>
       <c r="D637">
-        <v>0.009596928982725527</v>
+        <v>0.009596928982725529</v>
       </c>
     </row>
     <row r="638">
@@ -15558,7 +15558,7 @@
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C845">
@@ -16807,7 +16807,7 @@
         <v>16</v>
       </c>
       <c r="D914">
-        <v>0.0009032403748447555</v>
+        <v>0.0009032403748447556</v>
       </c>
     </row>
     <row r="915">
@@ -18301,7 +18301,7 @@
         <v>168</v>
       </c>
       <c r="D997">
-        <v>0.009484023935869933</v>
+        <v>0.009484023935869931</v>
       </c>
     </row>
     <row r="998">
@@ -19075,7 +19075,7 @@
         <v>16</v>
       </c>
       <c r="D1040">
-        <v>0.0009032403748447555</v>
+        <v>0.0009032403748447556</v>
       </c>
     </row>
     <row r="1041">
@@ -19525,7 +19525,7 @@
         <v>16</v>
       </c>
       <c r="D1065">
-        <v>0.0009032403748447555</v>
+        <v>0.0009032403748447556</v>
       </c>
     </row>
     <row r="1066">
@@ -20299,7 +20299,7 @@
         <v>16</v>
       </c>
       <c r="D1108">
-        <v>0.0009032403748447555</v>
+        <v>0.0009032403748447556</v>
       </c>
     </row>
     <row r="1109">
@@ -20731,7 +20731,7 @@
         <v>16</v>
       </c>
       <c r="D1132">
-        <v>0.0009032403748447555</v>
+        <v>0.0009032403748447556</v>
       </c>
     </row>
     <row r="1133">
@@ -24277,7 +24277,7 @@
         <v>16</v>
       </c>
       <c r="D1329">
-        <v>0.0009032403748447555</v>
+        <v>0.0009032403748447556</v>
       </c>
     </row>
     <row r="1330">
@@ -25105,7 +25105,7 @@
         <v>16</v>
       </c>
       <c r="D1375">
-        <v>0.0009032403748447555</v>
+        <v>0.0009032403748447556</v>
       </c>
     </row>
     <row r="1376">
